--- a/docs/case_files/CASE_AKE.xlsx
+++ b/docs/case_files/CASE_AKE.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" style="10" min="1" max="1"/>
@@ -791,54 +791,80 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
-    <row r="70"/>
-    <row r="71"/>
-    <row r="72"/>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>META (V5 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>v2.1 (52 cols, cold-start from CASE_PUMPBTC template — cols 51-52 CHƯA-TRA nhịp 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>consumer_rule</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Consumer đọc theo HEADER row 2 field names (không hardcode col index). Cols 42+ append-only per L-57.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>LAYER COVERAGE UPDATE (V4 21/08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>lsr_null_dates (57)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-05-01, 2026-05-02, 2026-05-03, 2026-05-04, 2026-05-05, 2026-05-06, 2026-05-07, 2026-05-08, 2026-05-09, 2026-05-10, 2026-05-11, 2026-05-12, 2026-05-13, 2026-05-14, 2026-05-15, 2026-05-16, 2026-05-17, 2026-05-18, 2026-05-19, 2026-05-20, 2026-05-21, 2026-05-22, 2026-05-23, 2026-05-24, 2026-05-25, 2026-05-26, 2026-05-27, 2026-05-28, 2026-05-29, 2026-05-30, 2026-05-31, 2026-06-01, 2026-06-02, 2026-06-03, 2026-06-04, 2026-06-05, 2026-06-06, 2026-06-07, 2026-06-08, 2026-06-09, 2026-06-10, 2026-06-11, 2026-06-12, 2026-06-13, 2026-06-14, 2026-06-15, 2026-06-16, 2026-06-17, 2026-06-18, 2026-06-19, 2026-06-20, 2026-06-21, 2026-06-22, 2026-06-23, 2026-06-24, 2026-06-25, 2026-06-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OI first_nn (real)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>OI last_nn</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12846,7 +12872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" style="10" min="1" max="2"/>
@@ -13156,7 +13182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -13166,7 +13192,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13178,7 +13203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -13199,7 +13224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
@@ -13220,7 +13245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
